--- a/outputs/Results/SWAT_res.xlsx
+++ b/outputs/Results/SWAT_res.xlsx
@@ -425,40 +425,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV3"/>
+  <dimension ref="A1:AN3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>target_optimization</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ablation</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>data</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>entity_id</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>ablation</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>downsample</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>mixerType</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>downsample</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>target_optimization</t>
-        </is>
-      </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>seed</t>
@@ -586,113 +586,73 @@
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>avgVUS_ROC</t>
+          <t>avggflops</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>avgVUS_PR</t>
+          <t>avgavgInfTime</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>avggflops</t>
+          <t>avgnParams</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>avgavgInfTime</t>
+          <t>alphas</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>avgnParams</t>
+          <t>f1_concat</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>alphas</t>
+          <t>TP_concat</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>f1_concat</t>
+          <t>FP_concat</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>TP_concat</t>
+          <t>TN_concat</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>FP_concat</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>TN_concat</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
           <t>FN_concat</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>avgAff_F1</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>avgAff_P</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>avgAff_R</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>avgRange_F1</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>avgRange_P</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>avgRange_R</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>pf1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>SWAT</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>causal</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>pf1</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -744,97 +704,85 @@
         <v>6</v>
       </c>
       <c r="W2" t="n">
-        <v>8894</v>
+        <v>8840</v>
       </c>
       <c r="X2" t="n">
-        <v>498</v>
+        <v>470</v>
       </c>
       <c r="Y2" t="n">
-        <v>78677</v>
+        <v>78705</v>
       </c>
       <c r="Z2" t="n">
-        <v>1892</v>
+        <v>1946</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.8245874281475988</v>
+        <v>0.8195809382532913</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9469761499148212</v>
+        <v>0.949516648764769</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.00628986422481844</v>
+        <v>0.005936217240290496</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.8815541679056399</v>
+        <v>0.8797770700636942</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.8692208116438351</v>
+        <v>0.8702631874488147</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.049051136</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>0.002319927919994701</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.049051136</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0.003084929151968523</v>
+        <v>43297</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
       </c>
       <c r="AJ2" t="n">
-        <v>43297</v>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
+        <v>0.8797770700636942</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>8840</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.8815541679056399</v>
+        <v>470</v>
       </c>
       <c r="AM2" t="n">
-        <v>8894</v>
+        <v>78705</v>
       </c>
       <c r="AN2" t="n">
-        <v>498</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>78677</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1892</v>
-      </c>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
+        <v>1946</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>sf1</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>SWAT</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>causal</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>sf1</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -886,84 +834,60 @@
         <v>6</v>
       </c>
       <c r="W3" t="n">
-        <v>8922</v>
+        <v>8945</v>
       </c>
       <c r="X3" t="n">
-        <v>491</v>
+        <v>513</v>
       </c>
       <c r="Y3" t="n">
-        <v>78684</v>
+        <v>78662</v>
       </c>
       <c r="Z3" t="n">
-        <v>1864</v>
+        <v>1841</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.8271833858705729</v>
+        <v>0.8293157797144447</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9478380962498673</v>
+        <v>0.945760203002749</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.006201452478686454</v>
+        <v>0.006479317966529839</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.8834100698054359</v>
+        <v>0.8837186326812884</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.9108655166002859</v>
+        <v>0.907629889003998</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.75814541015557</v>
+        <v>1.049051136</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.7791223285829483</v>
+        <v>0.001627777110446583</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.049051136</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0.001943861896341497</v>
+        <v>43297</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[0.00040306428093510684]</t>
+        </is>
       </c>
       <c r="AJ3" t="n">
-        <v>43297</v>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>[0.00040306428093510684]</t>
-        </is>
+        <v>0.8837186326812884</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>8945</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.8834100698054359</v>
+        <v>513</v>
       </c>
       <c r="AM3" t="n">
-        <v>8922</v>
+        <v>78662</v>
       </c>
       <c r="AN3" t="n">
-        <v>491</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>78684</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1864</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0.7813700720895614</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0.9527020911847508</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0.6622689603997062</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0.6814112371841322</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0.6314611824181093</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0.7399424105306459</v>
+        <v>1841</v>
       </c>
     </row>
   </sheetData>
